--- a/diseases/d091/2000-2004.xlsx
+++ b/diseases/d091/2000-2004.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -26145,7 +26145,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -26841,7 +26841,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -27537,7 +27537,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -29561,7 +29561,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -30257,7 +30257,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -30953,7 +30953,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -31649,7 +31649,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -33041,7 +33041,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -34433,7 +34433,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -35129,7 +35129,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -35825,7 +35825,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -36521,7 +36521,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
